--- a/files/result_analysis.xlsx
+++ b/files/result_analysis.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Above 95% Students" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Above 95%" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Best in Subject" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Subject-wise Averages" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +47,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -122,36 +136,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>16</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4762500" cy="4762500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -443,210 +427,609 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Sl. No.</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Percentage</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>KKRITIKA RAJPAL</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>98</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ANUSHKA UPADHYAY</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>96.8</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>VRINDA SAXENA</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>97.8</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ADITI SRIVASTAVA</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SUDHISH GUPTA</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>97.40000000000001</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AAKERSHITA RAJ</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>95.8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>PARI VAISH</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>97.40000000000001</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SHAMBHAVI PANDEY</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>95.40000000000001</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>PRIYA TRIPATHI</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>97.40000000000001</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GAURVI SHUKLA</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>95.2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>RUDRANSH AGARWAL</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>97</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ANNIKA AGRAWAL</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>95</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>SHIKSHA SRIVASTAVA</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>96.59999999999999</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SHAHNOOR</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>95</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>GAGAN MAKHEJA</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>96.2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>HARSHITA TANDON</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>96.2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ASMITA</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>NAVYA RAIZADA</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>95.8</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>SHREYA VERMA</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>95.59999999999999</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>MEENAL SRIVASTAVA</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>95.2</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>KHYATI SRIVASTAVA</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MANJARI TRIPATHI</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>95</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Top Score</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Topper(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>98</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PRANJAL SINGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>042</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>95</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SHREYANSH KRISHNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>043</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SHREYANSH KRISHNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>044</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ADITI SRIVASTAVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>049</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>FARIYA FATIMA, RISHU SINGH, SOUMY VERMA, VAIBHAVI, VAISHNAVI TIWARI, VIDHI MEHROTRA, AARYA MAURYA, ANANYA SRIVASTAVA, ANSHIKA KHETAN, MAITHILI AGARWAL, PRANJAL SINGH, SHIVI TRIPATHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>041</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>95</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SHREYANSH KRISHNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>048</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>93</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SHREY AGARWAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>87</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ADITI SINGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>037</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ADITI SRIVASTAVA, ANUSHKA SRIVASTAVA, DIPANSHI SINGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>083</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>96</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>HARSHAL JAISWAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>055</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>99</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SHAHNOOR, YUKTI TEKCHANDANI</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>97</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ANNIKA AGRAWAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>030</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>97</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>YUKTI TEKCHANDANI</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>027</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SHIVI TRIPATHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>029</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>98</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MAYANK MANI TRIPATHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>028</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>99</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ANUSHKA UPADHYAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>034</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>96</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ASTHA SHUKLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>036</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>69</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>KUSHAGRA SRIVASTAVA</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Subject Code</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Average Marks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>84.44</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>042</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>66.84</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>043</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>72.17</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>044</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>85.79000000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>049</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>96.36</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>041</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>67.65000000000001</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>048</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>78.17</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>73.36</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>037</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>85.40000000000001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>083</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>055</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>65.84</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>74.14</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>030</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>82.42</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>027</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>90.52</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>029</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>85.86</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>028</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>90.56</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>034</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>036</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/files/result_analysis.xlsx
+++ b/files/result_analysis.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,81 +445,121 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ANUSHKA UPADHYAY</t>
+          <t>OJASVI VED</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>96.8</v>
+        <v>97.83333333333333</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADITI SRIVASTAVA</t>
+          <t>ZOHA FATMA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>96.59999999999999</v>
+        <v>97.33333333333333</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AAKERSHITA RAJ</t>
+          <t>AVIKA SHARMA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>95.8</v>
+        <v>96.83333333333333</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SHAMBHAVI PANDEY</t>
+          <t>SWASTIK SHARMA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>95.40000000000001</v>
+        <v>96.33333333333333</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GAURVI SHUKLA</t>
+          <t>SWARA DWIVEDI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>95.2</v>
+        <v>96.33333333333333</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ANNIKA AGRAWAL</t>
+          <t>ZAINAB AHMAD</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>95</v>
+        <v>96.16666666666667</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SHAHNOOR</t>
+          <t>ANVITA KUMAR</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>95</v>
+        <v>95.83333333333333</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MANJARI TRIPATHI</t>
+          <t>ISHANK MISHRA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>95</v>
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ANUSHKA KASAUDHAN</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DIKSHA GUPTA</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>VAISHNAVI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>KUSHAGRA SRIVASTAVA</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>95.33333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -533,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,11 +600,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PRANJAL SINGH</t>
+          <t>DIVA GAUTAM, GARGI TRIPATHI, NETRITVA SINGH RAJPOOT, HARGUN SINGH, ANSH SRIVASTAVA, NAVYA SRIVASTAVA</t>
         </is>
       </c>
     </row>
@@ -575,11 +615,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SHREYANSH KRISHNA</t>
+          <t>SWASTIK SHARMA</t>
         </is>
       </c>
     </row>
@@ -594,7 +634,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SHREYANSH KRISHNA</t>
+          <t>HARSHIT DIXIT</t>
         </is>
       </c>
     </row>
@@ -605,11 +645,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ADITI SRIVASTAVA</t>
+          <t>KAADAMBARI RAJPAL</t>
         </is>
       </c>
     </row>
@@ -624,14 +664,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FARIYA FATIMA, RISHU SINGH, SOUMY VERMA, VAIBHAVI, VAISHNAVI TIWARI, VIDHI MEHROTRA, AARYA MAURYA, ANANYA SRIVASTAVA, ANSHIKA KHETAN, MAITHILI AGARWAL, PRANJAL SINGH, SHIVI TRIPATHI</t>
+          <t>AADYA TRIPATHI, ISHANK MISHRA, HARSHIT DIXIT, PRATHMESH, ZAINAB AHMAD, MINAKSHI SINGH VISEN, POOJA BEHERA, SAMRIDHI, VAISHNAVI, VEDIKA SRIVASTAVA</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>041</t>
+          <t>302</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -639,7 +679,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SHREYANSH KRISHNA</t>
+          <t>MEENAKSHI GOSWAMI</t>
         </is>
       </c>
     </row>
@@ -650,41 +690,41 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SHREY AGARWAL</t>
+          <t>DIKSHA GUPTA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>037</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ADITI SINGH</t>
+          <t>DIVYANSHI, NETRITVA SINGH RAJPOOT, HRITI TRIPATHI, OJASVI VED, ZAINAB AHMAD, ZOHA FATMA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>037</t>
+          <t>041</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ADITI SRIVASTAVA, ANUSHKA SRIVASTAVA, DIPANSHI SINGH</t>
+          <t>SWASTIK SHARMA</t>
         </is>
       </c>
     </row>
@@ -695,63 +735,63 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HARSHAL JAISWAL</t>
+          <t>ISHANK MISHRA, SWASTIK SHARMA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>055</t>
+          <t>844</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SHAHNOOR, YUKTI TEKCHANDANI</t>
+          <t>DIVA GAUTAM, HRITI TRIPATHI, LAKSHYA</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>028</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ANNIKA AGRAWAL</t>
+          <t>KUSHAGRA SRIVASTAVA, ZOHA FATMA</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>030</t>
+          <t>036</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>YUKTI TEKCHANDANI</t>
+          <t>DIVYANSHI</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>027</t>
+          <t>034</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -759,29 +799,29 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SHIVI TRIPATHI</t>
+          <t>MOHD AKHTAR MEHDI, TANVI SRIVASTAVA, OJASVI VED</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>029</t>
+          <t>836</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MAYANK MANI TRIPATHI</t>
+          <t>KAADAMBARI RAJPAL</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>028</t>
+          <t>055</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -789,37 +829,67 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ANUSHKA UPADHYAY</t>
+          <t>OJASVI VED</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>034</t>
+          <t>054</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ASTHA SHUKLA</t>
+          <t>ZAINAB AHMAD</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>036</t>
+          <t>030</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>KUSHAGRA SRIVASTAVA</t>
+          <t>DIKSHA GUPTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>027</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>97</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AVIKA SHARMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>029</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>100</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ZOHA FATMA</t>
         </is>
       </c>
     </row>
@@ -834,7 +904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -856,7 +926,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>84.44</v>
+        <v>88.95999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -866,7 +936,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>66.84</v>
+        <v>68.73999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -876,7 +946,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>72.17</v>
+        <v>75.38</v>
       </c>
     </row>
     <row r="5">
@@ -886,7 +956,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>85.79000000000001</v>
+        <v>80.38</v>
       </c>
     </row>
     <row r="6">
@@ -896,17 +966,17 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>96.36</v>
+        <v>97.52</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>041</t>
+          <t>302</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>67.65000000000001</v>
+        <v>78.26000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -916,27 +986,27 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>78.17</v>
+        <v>85.23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>037</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>73.36</v>
+        <v>88.28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>037</t>
+          <t>041</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>85.40000000000001</v>
+        <v>59.33</v>
       </c>
     </row>
     <row r="11">
@@ -946,87 +1016,107 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>81</v>
+        <v>81.53</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>055</t>
+          <t>844</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>65.84</v>
+        <v>94.03</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>028</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>74.14</v>
+        <v>85.09999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>030</t>
+          <t>036</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>82.42</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>027</t>
+          <t>034</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>90.52</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>029</t>
+          <t>836</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>85.86</v>
+        <v>93.67</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>028</t>
+          <t>055</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>90.56</v>
+        <v>66.34999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>034</t>
+          <t>054</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>94</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>036</t>
+          <t>030</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>69</v>
+        <v>76.38</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>027</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>80.76000000000001</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>029</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>79.97</v>
       </c>
     </row>
   </sheetData>
